--- a/Master/6150r00/6150r00 @ 0.250 IPR_cutlet_data.xlsx
+++ b/Master/6150r00/6150r00 @ 0.250 IPR_cutlet_data.xlsx
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1694,162 +1694,202 @@
     </row>
     <row r="63">
       <c r="A63" s="6" t="n">
-        <v>3.135</v>
+        <v>4.243</v>
       </c>
       <c r="B63" s="6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C63" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D63" s="7" t="n">
-        <v>8.2887</v>
+        <v>8.240500000000001</v>
       </c>
       <c r="E63" s="7" t="n">
-        <v>-1.5055</v>
+        <v>-3.4442</v>
       </c>
       <c r="F63" s="7" t="n">
-        <v>0.0157</v>
+        <v>0.0001</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="6" t="n">
-        <v>6.135</v>
+        <v>1.243</v>
       </c>
       <c r="B64" s="6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C64" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D64" s="7" t="n">
-        <v>8.2898</v>
+        <v>8.241400000000001</v>
       </c>
       <c r="E64" s="7" t="n">
-        <v>-1.3822</v>
+        <v>-3.5771</v>
       </c>
       <c r="F64" s="7" t="n">
-        <v>0.0154</v>
+        <v>0.0002</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="6" t="n">
-        <v>5.136</v>
+        <v>3.135</v>
       </c>
       <c r="B65" s="6" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C65" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D65" s="7" t="n">
-        <v>8.4049</v>
+        <v>8.2887</v>
       </c>
       <c r="E65" s="7" t="n">
-        <v>-1.6574</v>
+        <v>-1.5055</v>
       </c>
       <c r="F65" s="7" t="n">
-        <v>0.0134</v>
+        <v>0.0157</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="6" t="n">
-        <v>2.136</v>
+        <v>6.135</v>
       </c>
       <c r="B66" s="6" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C66" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D66" s="7" t="n">
-        <v>8.4053</v>
+        <v>8.2898</v>
       </c>
       <c r="E66" s="7" t="n">
-        <v>-1.7835</v>
+        <v>-1.3822</v>
       </c>
       <c r="F66" s="7" t="n">
-        <v>0.0135</v>
+        <v>0.0154</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="6" t="n">
-        <v>4.137</v>
+        <v>5.136</v>
       </c>
       <c r="B67" s="6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C67" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D67" s="7" t="n">
-        <v>8.5036</v>
+        <v>8.4049</v>
       </c>
       <c r="E67" s="7" t="n">
-        <v>-1.9404</v>
+        <v>-1.6574</v>
       </c>
       <c r="F67" s="7" t="n">
-        <v>0.0119</v>
+        <v>0.0134</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="6" t="n">
-        <v>1.137</v>
+        <v>2.136</v>
       </c>
       <c r="B68" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C68" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D68" s="7" t="n">
-        <v>8.504099999999999</v>
+        <v>8.4053</v>
       </c>
       <c r="E68" s="7" t="n">
-        <v>-2.0671</v>
+        <v>-1.7835</v>
       </c>
       <c r="F68" s="7" t="n">
-        <v>0.0106</v>
+        <v>0.0135</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="6" t="n">
+        <v>4.137</v>
+      </c>
+      <c r="B69" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C69" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D69" s="7" t="n">
+        <v>8.5036</v>
+      </c>
+      <c r="E69" s="7" t="n">
+        <v>-1.9404</v>
+      </c>
+      <c r="F69" s="7" t="n">
+        <v>0.0119</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="n">
+        <v>1.137</v>
+      </c>
+      <c r="B70" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C70" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D70" s="7" t="n">
+        <v>8.504099999999999</v>
+      </c>
+      <c r="E70" s="7" t="n">
+        <v>-2.0671</v>
+      </c>
+      <c r="F70" s="7" t="n">
+        <v>0.0106</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="n">
         <v>6.138</v>
       </c>
-      <c r="B69" s="6" t="n">
+      <c r="B71" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="C69" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D69" s="7" t="n">
+      <c r="C71" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D71" s="7" t="n">
         <v>8.5845</v>
       </c>
-      <c r="E69" s="7" t="n">
+      <c r="E71" s="7" t="n">
         <v>-2.107</v>
       </c>
-      <c r="F69" s="7" t="n">
+      <c r="F71" s="7" t="n">
         <v>0.0089</v>
       </c>
     </row>
-    <row r="71">
-      <c r="E71" s="8" t="inlineStr">
+    <row r="73">
+      <c r="E73" s="8" t="inlineStr">
         <is>
           <t>Count:</t>
         </is>
       </c>
-      <c r="F71" s="9" t="n">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="E72" s="8" t="inlineStr">
+      <c r="F73" s="9" t="n">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="E74" s="8" t="inlineStr">
         <is>
           <t>Total Area:</t>
         </is>
       </c>
-      <c r="F72" s="10" t="n">
-        <v>2.1353</v>
+      <c r="F74" s="10" t="n">
+        <v>2.1356</v>
       </c>
     </row>
   </sheetData>
